--- a/Data/Regression Evidence 2025/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -178,7 +178,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10700283</t>
+    <t>10700471</t>
   </si>
   <si>
     <t>Passed</t>
@@ -193,10 +193,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Orville</t>
-  </si>
-  <si>
-    <t>Turcotte</t>
+    <t>Janelle</t>
+  </si>
+  <si>
+    <t>Wolf</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -226,7 +226,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 10358277</t>
+    <t>Auto 32767878</t>
   </si>
   <si>
     <t>Regular</t>
@@ -283,16 +283,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10700268</t>
+    <t>10700467</t>
   </si>
   <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
   </si>
   <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>Feest</t>
+    <t>Ellsworth</t>
+  </si>
+  <si>
+    <t>Gorczany</t>
   </si>
   <si>
     <t>No</t>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L2" s="16">
         <f>TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>57</v>
@@ -1219,11 +1219,11 @@
       </c>
       <c r="X2" s="21">
         <f>L2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="Y2" s="16">
         <f>TODAY()+20</f>
-        <v>45873</v>
+        <v>45894</v>
       </c>
       <c r="Z2" s="22" t="s">
         <v>69</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AS2" s="30">
         <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>873062303</v>
+        <v>966207480</v>
       </c>
       <c r="AT2" s="24" t="s">
         <v>83</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L3" s="36">
         <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M3" s="28" t="s">
         <v>57</v>
@@ -1393,11 +1393,11 @@
       </c>
       <c r="X3" s="21">
         <f t="shared" ref="X3" si="1">L3</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="Y3" s="36">
         <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45873</v>
+        <v>45894</v>
       </c>
       <c r="Z3" s="39" t="s">
         <v>69</v>
@@ -1457,7 +1457,7 @@
         <v>82</v>
       </c>
       <c r="AS3" s="47">
-        <v>949795620</v>
+        <v>236805149</v>
       </c>
       <c r="AT3" s="41" t="s">
         <v>83</v>
